--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487418_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487418_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6205</v>
+        <v>5.8997</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3308</v>
+        <v>6.4496</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7103</v>
+        <v>-0.55</v>
       </c>
       <c r="G2" t="n">
         <v>3.3159</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2254</v>
+        <v>0.0538</v>
       </c>
       <c r="T2" t="n">
-        <v>0.117</v>
+        <v>0.2358</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3424</v>
+        <v>-0.182</v>
       </c>
       <c r="V2" t="n">
         <v>1.159</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4126</v>
+        <v>2.0269</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5755</v>
+        <v>3.6709</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1628</v>
+        <v>-1.644</v>
       </c>
       <c r="G3" t="n">
         <v>1.5664</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8048</v>
+        <v>0.419</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3803</v>
+        <v>0.4758</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4244</v>
+        <v>-0.0567</v>
       </c>
       <c r="V3" t="n">
         <v>1.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3195</v>
+        <v>0.7921</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7143</v>
+        <v>2.6948</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3948</v>
+        <v>-1.9027</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5132</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3454</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0098</v>
+        <v>-0.0294</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3552</v>
+        <v>0.8474</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8837</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0178</v>
+        <v>0.1469</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="G5" t="n">
         <v>0.1364</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1186</v>
+        <v>0.0104</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2368</v>
+        <v>-1.1077</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9792</v>
+        <v>-0.8769</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2575</v>
+        <v>-0.2308</v>
       </c>
       <c r="G6" t="n">
         <v>0.1364</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1186</v>
+        <v>0.0104</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9179</v>
+        <v>-2.4405</v>
       </c>
       <c r="E7" t="n">
-        <v>0.034</v>
+        <v>-0.5997</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.952</v>
+        <v>-1.8408</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9175</v>
+        <v>2.3149</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5934</v>
+        <v>-0.3321</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3241</v>
+        <v>2.647</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1658</v>
+        <v>5.2117</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3029</v>
+        <v>2.0448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4687</v>
+        <v>3.1668</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0833</v>
+        <v>-2.8967</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2905</v>
+        <v>-2.3769</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7927</v>
+        <v>-0.5198</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-4.7004</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-5.8755</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8244</v>
+        <v>0.4957</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8475</v>
+        <v>0.0641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0231</v>
+        <v>0.4316</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8249</v>
+        <v>-0.5507</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8249</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5592</v>
+        <v>-2.6981</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4778</v>
+        <v>0.0934</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0814</v>
+        <v>-2.7916</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3149</v>
+        <v>-1.9175</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3321</v>
+        <v>-1.5934</v>
       </c>
       <c r="I8" t="n">
-        <v>2.647</v>
+        <v>-0.3241</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2117</v>
+        <v>0.1658</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0448</v>
+        <v>-0.3029</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1668</v>
+        <v>0.4687</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8967</v>
+        <v>-2.0833</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3769</v>
+        <v>-1.2905</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5198</v>
+        <v>-0.7927</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.7004</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.8755</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.623</v>
+        <v>1.0442</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.9069</v>
       </c>
       <c r="U8" t="n">
-        <v>0.191</v>
+        <v>0.1373</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5507</v>
+        <v>-1.8249</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5507</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4004</v>
+        <v>-5.0306</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1199</v>
+        <v>-2.7768</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2805</v>
+        <v>-2.2538</v>
       </c>
       <c r="G9" t="n">
         <v>-1.637</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.101</v>
+        <v>-0.7312</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6693</v>
+        <v>0.0123</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7703</v>
+        <v>-0.7435</v>
       </c>
       <c r="V9" t="n">
         <v>0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3889</v>
+        <v>-5.2447</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.313</v>
+        <v>-4.3559</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0759</v>
+        <v>-0.8888</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4027</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2638</v>
+        <v>-1.1197</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2088</v>
+        <v>-0.2517</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0551</v>
+        <v>-0.8679</v>
       </c>
       <c r="V10" t="n">
         <v>0.3905</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5878</v>
+        <v>-7.4704</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4336</v>
+        <v>-4.4766</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1542</v>
+        <v>-2.9938</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0516</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0858</v>
+        <v>-0.9684</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>-0.1747</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.7937</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8837</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.7206</v>
+        <v>-15.1264</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6688999999999998</v>
+        <v>-0.07490000000000041</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.0516</v>
+        <v>-15.0517</v>
       </c>
       <c r="G12" t="n">
         <v>-1.052</v>
@@ -1387,16 +1387,16 @@
         <v>-22.5225</v>
       </c>
       <c r="R12" t="n">
-        <v>9.792200000000001</v>
+        <v>9.792199999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5616000000000001</v>
+        <v>0.0321999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8498000000000001</v>
+        <v>1.4437</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4116</v>
+        <v>-1.4113</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3769</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.0007</v>
+        <v>10.5383</v>
       </c>
       <c r="E13" t="n">
-        <v>9.93</v>
+        <v>7.6786</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0708</v>
+        <v>2.8597</v>
       </c>
       <c r="G13" t="n">
         <v>6.3795</v>
@@ -1468,13 +1468,13 @@
         <v>3.7211</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0705</v>
+        <v>1.6081</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6053</v>
+        <v>1.3539</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4653</v>
+        <v>0.2542</v>
       </c>
       <c r="V13" t="n">
         <v>1.7673</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2323</v>
+        <v>6.7276</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7796</v>
+        <v>6.0076</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4526</v>
+        <v>0.72</v>
       </c>
       <c r="G14" t="n">
         <v>3.0965</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.098</v>
+        <v>0.3973</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.414</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2841</v>
+        <v>-0.0168</v>
       </c>
       <c r="V14" t="n">
         <v>0.8837</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1653</v>
+        <v>4.7396</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6973</v>
+        <v>2.0043</v>
       </c>
       <c r="F15" t="n">
-        <v>2.468</v>
+        <v>2.7353</v>
       </c>
       <c r="G15" t="n">
         <v>2.0174</v>
@@ -1624,13 +1624,13 @@
         <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2023</v>
+        <v>0.372</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1653</v>
+        <v>0.4723</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3676</v>
+        <v>-0.1003</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4757</v>
+        <v>3.4489</v>
       </c>
       <c r="E16" t="n">
         <v>4.9283</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4526</v>
+        <v>-1.4793</v>
       </c>
       <c r="G16" t="n">
         <v>0.4904</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2106</v>
+        <v>-1.2373</v>
       </c>
       <c r="T16" t="n">
         <v>-0.891</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3195</v>
+        <v>-0.3463</v>
       </c>
       <c r="V16" t="n">
         <v>2.4332</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0891</v>
+        <v>3.0638</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2698</v>
+        <v>-0.6645</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3589</v>
+        <v>3.7283</v>
       </c>
       <c r="G17" t="n">
-        <v>1.688</v>
+        <v>0.2657</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4151</v>
+        <v>1.6009</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2729</v>
+        <v>-1.3352</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8068</v>
+        <v>-0.2269</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3629</v>
+        <v>2.0738</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5562</v>
+        <v>-2.3007</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1188</v>
+        <v>0.4926</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9479</v>
+        <v>-0.4729</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.9655</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>2.546</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3294</v>
+        <v>3.5253</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6765</v>
+        <v>0.252</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1941</v>
+        <v>0.5417</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4824</v>
+        <v>-0.2897</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1825</v>
+        <v>3.0311</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2785</v>
+        <v>-1.1675</v>
       </c>
       <c r="F18" t="n">
-        <v>3.461</v>
+        <v>4.1985</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2657</v>
+        <v>1.688</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6009</v>
+        <v>1.4151</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3352</v>
+        <v>0.2729</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2269</v>
+        <v>1.8068</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0738</v>
+        <v>2.3629</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.3007</v>
+        <v>-0.5562</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4926</v>
+        <v>-0.1188</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4729</v>
+        <v>-0.9479</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9655</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>2.546</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5253</v>
+        <v>3.3294</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6293</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0723</v>
+        <v>0.2964</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9043</v>
+        <v>1.5688</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6587</v>
+        <v>2.454</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7544</v>
+        <v>-0.8852</v>
       </c>
       <c r="G19" t="n">
         <v>3.0197</v>
@@ -1936,13 +1936,13 @@
         <v>2.3502</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2905</v>
+        <v>-0.6261</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2682</v>
+        <v>-0.4729</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0223</v>
+        <v>-0.1532</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6696</v>
+        <v>0.3967</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7319</v>
+        <v>0.3225</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0623</v>
+        <v>0.0742</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0714</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8781</v>
+        <v>0.6052</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0675</v>
+        <v>0.6581</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1894</v>
+        <v>-0.0529</v>
       </c>
       <c r="V20" t="n">
         <v>0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9832</v>
+        <v>-2.4374</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2043</v>
+        <v>0.6136</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1874</v>
+        <v>-3.051</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9037</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7834</v>
+        <v>-0.2376</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.594</v>
+        <v>-0.1847</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1894</v>
+        <v>-0.0529</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9871</v>
+        <v>-5.9382</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1339</v>
+        <v>-3.0316</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8532</v>
+        <v>-2.9066</v>
       </c>
       <c r="G22" t="n">
         <v>-5.6973</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4867</v>
+        <v>-0.4379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8316</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3449</v>
+        <v>0.2914</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3905</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.028700000000001</v>
+        <v>-8.7364</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5878</v>
+        <v>-3.4854</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4409</v>
+        <v>-5.251</v>
       </c>
       <c r="G23" t="n">
         <v>-6.2329</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3625</v>
+        <v>-0.0703</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1494</v>
+        <v>-0.0471</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2131</v>
+        <v>-0.0232</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4332</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.7205</v>
+        <v>16.4028</v>
       </c>
       <c r="E24" t="n">
-        <v>15.6601</v>
+        <v>15.6599</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06050000000000111</v>
+        <v>0.7428999999999988</v>
       </c>
       <c r="G24" t="n">
         <v>1.051899999999999</v>
@@ -2326,13 +2326,13 @@
         <v>22.5224</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5618000000000005</v>
+        <v>1.2438</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4117</v>
+        <v>1.4114</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8498000000000001</v>
+        <v>-0.1677</v>
       </c>
       <c r="V24" t="n">
         <v>1.3768</v>
